--- a/Config/DataTables/Datas/Entity/#Hero.xlsx
+++ b/Config/DataTables/Datas/Entity/#Hero.xlsx
@@ -1149,8 +1149,8 @@
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="7" customWidth="1"/>
     <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="14.375" customWidth="1"/>
-    <col min="12" max="12" width="8.75" customWidth="1"/>
+    <col min="11" max="11" width="16.875" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
     <col min="13" max="13" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1394,7 +1394,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="9">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L5" s="9">
         <v>1000</v>

--- a/Config/DataTables/Datas/Entity/#Hero.xlsx
+++ b/Config/DataTables/Datas/Entity/#Hero.xlsx
@@ -641,162 +641,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -805,17 +803,14 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1139,26 +1134,26 @@
   <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="8.81666666666667" customWidth="1"/>
-    <col min="3" max="3" width="11.6416666666667" customWidth="1"/>
-    <col min="4" max="4" width="37.625" customWidth="1"/>
-    <col min="5" max="5" width="13.375"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="7" width="8.875" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="16.875" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="14.875" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6416666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1208,10 +1203,10 @@
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1261,7 +1256,7 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1314,10 +1309,10 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1365,8 +1360,8 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2">
         <v>1000001</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1390,14 +1385,14 @@
       <c r="I5" s="8">
         <v>100</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="6">
         <v>1</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="6">
         <v>700</v>
       </c>
-      <c r="L5" s="9">
-        <v>1000</v>
+      <c r="L5" s="6">
+        <v>500</v>
       </c>
       <c r="M5" s="6">
         <v>100</v>
